--- a/diseases/d020/2000-2004.xlsx
+++ b/diseases/d020/2000-2004.xlsx
@@ -36115,11 +36115,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36132,7 +36127,7 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
@@ -36142,15 +36137,15 @@
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
+          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS; SER_CN_PROV_REPORT_JAPANESE_ENCEPHALITIS</t>
         </is>
       </c>
       <c r="AT210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -36366,7 +36361,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
@@ -36376,15 +36371,15 @@
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
+          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS; SER_CN_PROV_REPORT_JAPANESE_ENCEPHALITIS</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -45229,11 +45224,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45246,7 +45236,7 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
@@ -45256,15 +45246,15 @@
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
+          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS; SER_CN_PROV_REPORT_JAPANESE_ENCEPHALITIS</t>
         </is>
       </c>
       <c r="AT258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
@@ -45480,7 +45470,7 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
@@ -45490,15 +45480,15 @@
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
+          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS; SER_CN_PROV_REPORT_JAPANESE_ENCEPHALITIS</t>
         </is>
       </c>
       <c r="AT259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
@@ -53948,11 +53938,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
       <c r="AA304" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53965,7 +53950,7 @@
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ304" t="inlineStr">
@@ -53975,15 +53960,15 @@
       </c>
       <c r="AS304" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
+          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS; SER_CN_PROV_REPORT_JAPANESE_ENCEPHALITIS</t>
         </is>
       </c>
       <c r="AT304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
@@ -54199,7 +54184,7 @@
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ305" t="inlineStr">
@@ -54209,15 +54194,15 @@
       </c>
       <c r="AS305" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS</t>
+          <t>SER_CN_PROV_DC_JAPANESE_ENCEPHALITIS; SER_CN_PROV_REPORT_JAPANESE_ENCEPHALITIS</t>
         </is>
       </c>
       <c r="AT305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
